--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -15241,16 +15241,16 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>8047</v>
+        <v>8050</v>
       </c>
       <c r="O84" t="n">
-        <v>8047</v>
+        <v>8050</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>29.55511671167575</v>
+        <v>29.56613514713431</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16773,16 +16773,16 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1352</v>
+        <v>1658</v>
       </c>
       <c r="O93" t="n">
-        <v>1352</v>
+        <v>1658</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>4.965641579990756</v>
+        <v>6.089521996763811</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>458367</v>
+        <v>458676</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -15241,16 +15241,16 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>8050</v>
+        <v>8053</v>
       </c>
       <c r="O84" t="n">
-        <v>8050</v>
+        <v>8053</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>29.56613514713431</v>
+        <v>29.57715358259287</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -15389,16 +15389,16 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="O85" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>18.28615827648333</v>
+        <v>18.32173445990061</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -15551,10 +15551,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="O86" t="n">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -16773,16 +16773,16 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1658</v>
+        <v>1938</v>
       </c>
       <c r="O93" t="n">
-        <v>1658</v>
+        <v>1938</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>6.089521996763811</v>
+        <v>7.117909306229354</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16921,16 +16921,16 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="O94" t="n">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="Q94" t="n">
         <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>1.956690087950551</v>
+        <v>3.860015900775179</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17083,10 +17083,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="O95" t="n">
-        <v>110</v>
+        <v>217</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>458676</v>
+        <v>459068</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13303,16 +13303,16 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="O73" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="Q73" t="n">
         <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>28.00886293565792</v>
+        <v>28.01253574747744</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -15241,16 +15241,16 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>8053</v>
+        <v>8071</v>
       </c>
       <c r="O84" t="n">
-        <v>8053</v>
+        <v>8071</v>
       </c>
       <c r="Q84" t="n">
         <v>0</v>
       </c>
       <c r="R84" t="n">
-        <v>29.57715358259287</v>
+        <v>29.64326419534422</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16773,16 +16773,16 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>1938</v>
+        <v>2213</v>
       </c>
       <c r="O93" t="n">
-        <v>1938</v>
+        <v>2213</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>7.117909306229354</v>
+        <v>8.127932556597296</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17576,7 +17576,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>459068</v>
+        <v>459362</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>3261</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>1131</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>12.55578777410417</v>
       </c>
@@ -1454,9 +1448,6 @@
       <c r="O6" t="n">
         <v>976</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>17.36117750763398</v>
       </c>
@@ -1850,9 +1841,6 @@
       <c r="O8" t="n">
         <v>135</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>33.55462817743688</v>
       </c>
@@ -2256,9 +2244,6 @@
       <c r="O10" t="n">
         <v>2269</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>21.20353369177491</v>
       </c>
@@ -3540,9 +3525,6 @@
       <c r="O18" t="n">
         <v>2841</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3933,9 +3915,6 @@
       <c r="O20" t="n">
         <v>1061</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>11.77868331416846</v>
       </c>
@@ -4081,9 +4060,6 @@
       <c r="O21" t="n">
         <v>911</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>16.20495154657229</v>
       </c>
@@ -4477,9 +4453,6 @@
       <c r="O23" t="n">
         <v>123</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>30.57199456166471</v>
       </c>
@@ -4883,9 +4856,6 @@
       <c r="O25" t="n">
         <v>2156</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>20.14756220337889</v>
       </c>
@@ -6019,9 +5989,6 @@
       <c r="O32" t="n">
         <v>3155</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6412,9 +6379,6 @@
       <c r="O34" t="n">
         <v>1220</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>13.54382058745101</v>
       </c>
@@ -6560,9 +6524,6 @@
       <c r="O35" t="n">
         <v>885</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>15.74246116214762</v>
       </c>
@@ -6956,9 +6917,6 @@
       <c r="O37" t="n">
         <v>136</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>33.80318097875122</v>
       </c>
@@ -7362,9 +7320,6 @@
       <c r="O39" t="n">
         <v>2189</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>20.45594325751225</v>
       </c>
@@ -8350,9 +8305,6 @@
       <c r="O45" t="n">
         <v>7419</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>27.24859088901732</v>
       </c>
@@ -8498,9 +8450,6 @@
       <c r="O46" t="n">
         <v>3109</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8891,9 +8840,6 @@
       <c r="O48" t="n">
         <v>1027</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>11.4012325764854</v>
       </c>
@@ -9039,9 +8985,6 @@
       <c r="O49" t="n">
         <v>815</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>14.49729474254272</v>
       </c>
@@ -9435,9 +9378,6 @@
       <c r="O51" t="n">
         <v>97</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>24.10962172749168</v>
       </c>
@@ -9841,9 +9781,6 @@
       <c r="O53" t="n">
         <v>1904</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>17.79265233545149</v>
       </c>
@@ -10829,9 +10766,6 @@
       <c r="O59" t="n">
         <v>7584</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>27.85460483923809</v>
       </c>
@@ -10977,9 +10911,6 @@
       <c r="O60" t="n">
         <v>2872</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="S60" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11370,9 +11301,6 @@
       <c r="O62" t="n">
         <v>834</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>14.83526848500691</v>
       </c>
@@ -11766,9 +11694,6 @@
       <c r="O64" t="n">
         <v>125</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>31.0691001642934</v>
       </c>
@@ -12172,9 +12097,6 @@
       <c r="O66" t="n">
         <v>2043</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>19.09159071498287</v>
       </c>
@@ -13160,9 +13082,6 @@
       <c r="O72" t="n">
         <v>6938</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>1.9877634565154</v>
       </c>
@@ -13308,9 +13227,6 @@
       <c r="O73" t="n">
         <v>7627</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>28.01253574747744</v>
       </c>
@@ -13456,9 +13372,6 @@
       <c r="O74" t="n">
         <v>909</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>16.16937536315501</v>
       </c>
@@ -13852,9 +13765,6 @@
       <c r="O76" t="n">
         <v>153</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>38.02857860109512</v>
       </c>
@@ -14253,16 +14163,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="O78" t="n">
-        <v>2092</v>
-      </c>
-      <c r="Q78" t="n">
-        <v>0</v>
+        <v>2091</v>
       </c>
       <c r="R78" t="n">
-        <v>19.54948985596876</v>
+        <v>19.54014497554047</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -14415,10 +14322,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="O79" t="n">
-        <v>2092</v>
+        <v>2091</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
@@ -14654,9 +14561,6 @@
       <c r="O80" t="n">
         <v>12263</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>3.513396262215097</v>
       </c>
@@ -14802,9 +14706,6 @@
       <c r="O81" t="n">
         <v>13313</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>3.814225266155883</v>
       </c>
@@ -14950,9 +14851,6 @@
       <c r="O82" t="n">
         <v>12631</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>3.618829665501011</v>
       </c>
@@ -15098,9 +14996,6 @@
       <c r="O83" t="n">
         <v>10277</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>2.944399689047097</v>
       </c>
@@ -15246,9 +15141,6 @@
       <c r="O84" t="n">
         <v>8071</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>29.64326419534422</v>
       </c>
@@ -15394,9 +15286,6 @@
       <c r="O85" t="n">
         <v>1030</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>18.32173445990061</v>
       </c>
@@ -15785,16 +15674,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="O87" t="n">
-        <v>2312</v>
-      </c>
-      <c r="Q87" t="n">
-        <v>0</v>
+        <v>2308</v>
       </c>
       <c r="R87" t="n">
-        <v>21.6053635501911</v>
+        <v>21.56798402847796</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15947,10 +15833,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="O88" t="n">
-        <v>2312</v>
+        <v>2308</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16186,9 +16072,6 @@
       <c r="O89" t="n">
         <v>10203</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>2.923198406864604</v>
       </c>
@@ -16334,9 +16217,6 @@
       <c r="O90" t="n">
         <v>13432</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>3.848319219935838</v>
       </c>
@@ -16482,9 +16362,6 @@
       <c r="O91" t="n">
         <v>13446</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>3.852330273321715</v>
       </c>
@@ -16630,9 +16507,6 @@
       <c r="O92" t="n">
         <v>14046</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>4.024232561287879</v>
       </c>
@@ -16778,9 +16652,6 @@
       <c r="O93" t="n">
         <v>2213</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>8.127932556597296</v>
       </c>
@@ -16921,16 +16792,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="O94" t="n">
-        <v>217</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="R94" t="n">
-        <v>3.860015900775179</v>
+        <v>4.358082468617137</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17083,10 +16951,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="O95" t="n">
-        <v>217</v>
+        <v>245</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -17322,9 +17190,6 @@
       <c r="O96" t="n">
         <v>15153</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>4.341392282585449</v>
       </c>
@@ -17393,6 +17258,151 @@
         </is>
       </c>
       <c r="BC96" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>14684</v>
+      </c>
+      <c r="O97" t="n">
+        <v>14684</v>
+      </c>
+      <c r="R97" t="n">
+        <v>4.207021994158565</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17431,7 +17441,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -17514,7 +17524,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -17524,7 +17534,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -17576,7 +17586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>459362</v>
+        <v>474069</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16792,13 +16792,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="O94" t="n">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="R94" t="n">
-        <v>4.358082468617137</v>
+        <v>5.265275145757847</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="O95" t="n">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474069</v>
+        <v>474120</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7627</v>
+        <v>7628</v>
       </c>
       <c r="O73" t="n">
-        <v>7627</v>
+        <v>7628</v>
       </c>
       <c r="R73" t="n">
-        <v>28.01253574747744</v>
+        <v>28.01620855929696</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -15136,13 +15136,13 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>8071</v>
+        <v>8081</v>
       </c>
       <c r="O84" t="n">
-        <v>8071</v>
+        <v>8081</v>
       </c>
       <c r="R84" t="n">
-        <v>29.64326419534422</v>
+        <v>29.67999231353942</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -16647,13 +16647,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2213</v>
+        <v>2966</v>
       </c>
       <c r="O93" t="n">
-        <v>2213</v>
+        <v>2966</v>
       </c>
       <c r="R93" t="n">
-        <v>8.127932556597296</v>
+        <v>10.8935598566957</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16792,13 +16792,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="O94" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="R94" t="n">
-        <v>5.265275145757847</v>
+        <v>5.745553621891164</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="O95" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="U95" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474120</v>
+        <v>474911</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="O3" t="n">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="O4" t="n">
-        <v>3261</v>
+        <v>3263</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2841</v>
+        <v>2844</v>
       </c>
       <c r="O18" t="n">
-        <v>2841</v>
+        <v>2844</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -3676,10 +3676,10 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2841</v>
+        <v>2844</v>
       </c>
       <c r="O19" t="n">
-        <v>2841</v>
+        <v>2844</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="O32" t="n">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="O33" t="n">
-        <v>3155</v>
+        <v>3158</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -8445,10 +8445,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="O46" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="O47" t="n">
-        <v>3109</v>
+        <v>3110</v>
       </c>
       <c r="U47" t="inlineStr">
         <is>
@@ -10906,10 +10906,10 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="O60" t="n">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -11062,10 +11062,10 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="O61" t="n">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="U61" t="inlineStr">
         <is>
@@ -13328,12 +13328,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13367,22 +13367,19 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>909</v>
+        <v>3092</v>
       </c>
       <c r="O74" t="n">
-        <v>909</v>
-      </c>
-      <c r="R74" t="n">
-        <v>16.16937536315501</v>
+        <v>3092</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -13402,12 +13399,12 @@
       </c>
       <c r="AQ74" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT74" t="n">
@@ -13415,47 +13412,47 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13487,12 +13484,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13526,29 +13523,29 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>909</v>
+        <v>3092</v>
       </c>
       <c r="O75" t="n">
-        <v>909</v>
+        <v>3092</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Chlamydia</t>
+          <t>Chlamydial Infections</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
@@ -13558,7 +13555,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -13573,7 +13570,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD75" t="inlineStr">
@@ -13608,17 +13605,17 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN75" t="b">
@@ -13636,12 +13633,12 @@
       </c>
       <c r="AQ75" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT75" t="n">
@@ -13649,47 +13646,47 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13721,12 +13718,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13760,13 +13757,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>153</v>
+        <v>909</v>
       </c>
       <c r="O76" t="n">
-        <v>153</v>
+        <v>909</v>
       </c>
       <c r="R76" t="n">
-        <v>38.02857860109512</v>
+        <v>16.16937536315501</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13775,7 +13772,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -13790,7 +13787,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -13798,62 +13795,57 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -13885,12 +13877,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -13924,29 +13916,29 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>153</v>
+        <v>909</v>
       </c>
       <c r="O77" t="n">
-        <v>153</v>
+        <v>909</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>SRC_IS_DOH_STI</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Klamydía</t>
+          <t>Chlamydia</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -13956,7 +13948,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>laboratory_and_registry_diagnoses</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -13971,7 +13963,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>country:IS:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD77" t="inlineStr">
@@ -14006,17 +13998,17 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>IS_DOH_sti_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN77" t="b">
@@ -14029,7 +14021,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14037,62 +14029,57 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14124,12 +14111,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14163,13 +14150,13 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>2091</v>
+        <v>153</v>
       </c>
       <c r="O78" t="n">
-        <v>2091</v>
+        <v>153</v>
       </c>
       <c r="R78" t="n">
-        <v>19.54014497554047</v>
+        <v>38.02857860109512</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
@@ -14178,7 +14165,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -14193,65 +14180,70 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ78" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR78" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -14283,12 +14275,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14322,29 +14314,29 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>2091</v>
+        <v>153</v>
       </c>
       <c r="O79" t="n">
-        <v>2091</v>
+        <v>153</v>
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Klamydía</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -14354,7 +14346,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -14369,7 +14361,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
@@ -14404,12 +14396,12 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
@@ -14427,65 +14419,70 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ79" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -14517,12 +14514,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14547,7 +14544,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -14556,81 +14553,95 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>12263</v>
+        <v>2091</v>
       </c>
       <c r="O80" t="n">
-        <v>12263</v>
+        <v>2091</v>
       </c>
       <c r="R80" t="n">
-        <v>3.513396262215097</v>
+        <v>19.54014497554047</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ80" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14657,17 +14668,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14692,7 +14703,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -14701,81 +14712,170 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>13313</v>
+        <v>2091</v>
       </c>
       <c r="O81" t="n">
-        <v>13313</v>
-      </c>
-      <c r="R81" t="n">
-        <v>3.814225266155883</v>
-      </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2091</v>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE81" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG81" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN81" t="b">
+        <v>1</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ81" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -14837,7 +14937,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -14846,13 +14946,13 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>12631</v>
+        <v>12263</v>
       </c>
       <c r="O82" t="n">
-        <v>12631</v>
+        <v>12263</v>
       </c>
       <c r="R82" t="n">
-        <v>3.618829665501011</v>
+        <v>3.513396262215097</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
@@ -14982,7 +15082,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -14991,13 +15091,13 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>10277</v>
+        <v>13313</v>
       </c>
       <c r="O83" t="n">
-        <v>10277</v>
+        <v>13313</v>
       </c>
       <c r="R83" t="n">
-        <v>2.944399689047097</v>
+        <v>3.814225266155883</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
@@ -15097,12 +15197,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15127,22 +15227,22 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N84" t="n">
-        <v>8081</v>
+        <v>12631</v>
       </c>
       <c r="O84" t="n">
-        <v>8081</v>
+        <v>12631</v>
       </c>
       <c r="R84" t="n">
-        <v>29.67999231353942</v>
+        <v>3.618829665501011</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
@@ -15175,42 +15275,42 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15242,12 +15342,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15272,104 +15372,90 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N85" t="n">
-        <v>1030</v>
+        <v>10277</v>
       </c>
       <c r="O85" t="n">
-        <v>1030</v>
+        <v>10277</v>
       </c>
       <c r="R85" t="n">
-        <v>18.32173445990061</v>
+        <v>2.944399689047097</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -15396,17 +15482,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15440,170 +15526,81 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>1030</v>
+        <v>8081</v>
       </c>
       <c r="O86" t="n">
-        <v>1030</v>
-      </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA86" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
+        <v>8081</v>
+      </c>
+      <c r="R86" t="n">
+        <v>29.67999231353942</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP86" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR86" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr"/>
+      <c r="AT86" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV86" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP86" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ86" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT86" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV86" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15635,12 +15632,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15674,13 +15671,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>2308</v>
+        <v>1030</v>
       </c>
       <c r="O87" t="n">
-        <v>2308</v>
+        <v>1030</v>
       </c>
       <c r="R87" t="n">
-        <v>21.56798402847796</v>
+        <v>18.32173445990061</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15689,7 +15686,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15709,12 +15706,12 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -15722,47 +15719,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15794,12 +15791,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15833,29 +15830,29 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>2308</v>
+        <v>1030</v>
       </c>
       <c r="O88" t="n">
-        <v>2308</v>
+        <v>1030</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Klamydiainfektion</t>
+          <t>Chlamydia</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -15880,7 +15877,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -15915,17 +15912,17 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -15943,12 +15940,12 @@
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT88" t="n">
@@ -15956,47 +15953,47 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16028,12 +16025,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -16058,7 +16055,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -16067,81 +16064,95 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>10203</v>
+        <v>2308</v>
       </c>
       <c r="O89" t="n">
-        <v>10203</v>
+        <v>2308</v>
       </c>
       <c r="R89" t="n">
-        <v>2.923198406864604</v>
+        <v>21.56798402847796</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS89" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ89" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS89" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16168,17 +16179,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -16203,7 +16214,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -16212,81 +16223,170 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>13432</v>
+        <v>2308</v>
       </c>
       <c r="O90" t="n">
-        <v>13432</v>
-      </c>
-      <c r="R90" t="n">
-        <v>3.848319219935838</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2308</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -16348,7 +16448,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -16357,13 +16457,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="O91" t="n">
-        <v>13446</v>
+        <v>10203</v>
       </c>
       <c r="R91" t="n">
-        <v>3.852330273321715</v>
+        <v>2.923198406864604</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16493,7 +16593,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -16502,13 +16602,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="O92" t="n">
-        <v>14046</v>
+        <v>13432</v>
       </c>
       <c r="R92" t="n">
-        <v>4.024232561287879</v>
+        <v>3.848319219935838</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16608,12 +16708,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -16638,22 +16738,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>2966</v>
+        <v>13446</v>
       </c>
       <c r="O93" t="n">
-        <v>2966</v>
+        <v>13446</v>
       </c>
       <c r="R93" t="n">
-        <v>10.8935598566957</v>
+        <v>3.852330273321715</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -16686,42 +16786,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16753,12 +16853,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -16783,104 +16883,90 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>323</v>
+        <v>14046</v>
       </c>
       <c r="O94" t="n">
-        <v>323</v>
+        <v>14046</v>
       </c>
       <c r="R94" t="n">
-        <v>5.745553621891164</v>
+        <v>4.024232561287879</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -16907,17 +16993,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -16951,170 +17037,81 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>323</v>
+        <v>3376</v>
       </c>
       <c r="O95" t="n">
-        <v>323</v>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA95" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
+        <v>3376</v>
+      </c>
+      <c r="R95" t="n">
+        <v>12.39941270269881</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR95" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr"/>
+      <c r="AT95" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP95" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ95" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV95" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17146,12 +17143,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17185,81 +17182,95 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>15153</v>
+        <v>323</v>
       </c>
       <c r="O96" t="n">
-        <v>15153</v>
+        <v>323</v>
       </c>
       <c r="R96" t="n">
-        <v>4.341392282585449</v>
+        <v>5.745553621891164</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -17286,123 +17297,502 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>323</v>
+      </c>
+      <c r="O97" t="n">
+        <v>323</v>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD97" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE97" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG97" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH97" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM97" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN97" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>D094</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Chlamydia trachomatis infection</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
         <is>
           <t>沙眼衣原体感染</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>15153</v>
+      </c>
+      <c r="O98" t="n">
+        <v>15153</v>
+      </c>
+      <c r="R98" t="n">
+        <v>4.341392282585449</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
+      <c r="AT98" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N97" t="n">
+      <c r="N99" t="n">
         <v>14684</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O99" t="n">
         <v>14684</v>
       </c>
-      <c r="R97" t="n">
+      <c r="R99" t="n">
         <v>4.207021994158565</v>
       </c>
-      <c r="S97" t="inlineStr">
+      <c r="S99" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO97" t="inlineStr">
+      <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP97" t="inlineStr">
+      <c r="AP99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR97" t="inlineStr">
+      <c r="AR99" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS97" t="inlineStr"/>
-      <c r="AT97" t="n">
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
         <v>0</v>
       </c>
-      <c r="AU97" t="inlineStr">
+      <c r="AU99" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV97" t="inlineStr">
+      <c r="AV99" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW97" t="inlineStr">
+      <c r="AW99" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
+      <c r="AX99" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY97" t="inlineStr">
+      <c r="AY99" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
+      <c r="AZ99" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA97" t="inlineStr">
+      <c r="BA99" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB97" t="inlineStr">
+      <c r="BB99" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC97" t="inlineStr">
+      <c r="BC99" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17524,7 +17914,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -17534,7 +17924,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="11">
@@ -17554,7 +17944,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -17586,7 +17976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>474911</v>
+        <v>478421</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>3376</v>
+        <v>3621</v>
       </c>
       <c r="O95" t="n">
-        <v>3376</v>
+        <v>3621</v>
       </c>
       <c r="R95" t="n">
-        <v>12.39941270269881</v>
+        <v>13.29925159848116</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="O96" t="n">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="R96" t="n">
-        <v>5.745553621891164</v>
+        <v>7.488786609338019</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="O97" t="n">
-        <v>323</v>
+        <v>421</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>478421</v>
+        <v>478764</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13757,13 +13757,13 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="O76" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="R76" t="n">
-        <v>16.16937536315501</v>
+        <v>16.18716345486365</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -13916,10 +13916,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="O77" t="n">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="U77" t="inlineStr">
         <is>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O87" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="R87" t="n">
-        <v>18.32173445990061</v>
+        <v>18.33952255160926</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O88" t="n">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="O96" t="n">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="R96" t="n">
-        <v>7.488786609338019</v>
+        <v>8.395979286478729</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="O97" t="n">
-        <v>421</v>
+        <v>472</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17976,7 +17976,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>478764</v>
+        <v>478817</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7628</v>
+        <v>7623</v>
       </c>
       <c r="O73" t="n">
-        <v>7628</v>
+        <v>7623</v>
       </c>
       <c r="R73" t="n">
-        <v>28.01620855929696</v>
+        <v>27.99784450019936</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="O80" t="n">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="R80" t="n">
-        <v>19.54014497554047</v>
+        <v>19.51211033425562</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="O81" t="n">
-        <v>2091</v>
+        <v>2088</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -16064,13 +16064,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="O89" t="n">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="R89" t="n">
-        <v>21.56798402847796</v>
+        <v>21.42781082205371</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16223,10 +16223,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="O90" t="n">
-        <v>2308</v>
+        <v>2293</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>3621</v>
+        <v>4239</v>
       </c>
       <c r="O95" t="n">
-        <v>3621</v>
+        <v>4239</v>
       </c>
       <c r="R95" t="n">
-        <v>13.29925159848116</v>
+        <v>15.56904930294439</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="O96" t="n">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="R96" t="n">
-        <v>8.395979286478729</v>
+        <v>8.947410129446611</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="O97" t="n">
-        <v>472</v>
+        <v>503</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17793,6 +17793,151 @@
         </is>
       </c>
       <c r="BC99" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>14554</v>
+      </c>
+      <c r="O100" t="n">
+        <v>14554</v>
+      </c>
+      <c r="R100" t="n">
+        <v>4.169776498432563</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17831,7 +17976,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -17914,7 +18059,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10">
@@ -17924,7 +18069,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -17976,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>478817</v>
+        <v>493997</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>8081</v>
+        <v>8080</v>
       </c>
       <c r="O86" t="n">
-        <v>8081</v>
+        <v>8080</v>
       </c>
       <c r="R86" t="n">
-        <v>29.67999231353942</v>
+        <v>29.6763195017199</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4239</v>
+        <v>4569</v>
       </c>
       <c r="O95" t="n">
-        <v>4239</v>
+        <v>4569</v>
       </c>
       <c r="R95" t="n">
-        <v>15.56904930294439</v>
+        <v>16.78107720338592</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="O96" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="R96" t="n">
-        <v>8.947410129446611</v>
+        <v>9.676721889500909</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="O97" t="n">
-        <v>503</v>
+        <v>544</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>493997</v>
+        <v>494367</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="O87" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="R87" t="n">
-        <v>18.33952255160926</v>
+        <v>18.3573106433179</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="O88" t="n">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4569</v>
+        <v>4664</v>
       </c>
       <c r="O95" t="n">
-        <v>4569</v>
+        <v>4664</v>
       </c>
       <c r="R95" t="n">
-        <v>16.78107720338592</v>
+        <v>17.1299943262403</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="O96" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="R96" t="n">
-        <v>9.676721889500909</v>
+        <v>10.56612647493298</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="O97" t="n">
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494367</v>
+        <v>494513</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>8080</v>
+        <v>8083</v>
       </c>
       <c r="O86" t="n">
-        <v>8080</v>
+        <v>8083</v>
       </c>
       <c r="R86" t="n">
-        <v>29.6763195017199</v>
+        <v>29.68733793717847</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4664</v>
+        <v>4733</v>
       </c>
       <c r="O95" t="n">
-        <v>4664</v>
+        <v>4733</v>
       </c>
       <c r="R95" t="n">
-        <v>17.1299943262403</v>
+        <v>17.38341834178717</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494513</v>
+        <v>494585</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4733</v>
+        <v>4981</v>
       </c>
       <c r="O95" t="n">
-        <v>4733</v>
+        <v>4981</v>
       </c>
       <c r="R95" t="n">
-        <v>17.38341834178717</v>
+        <v>18.29427567302807</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494585</v>
+        <v>494833</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7623</v>
+        <v>7626</v>
       </c>
       <c r="O73" t="n">
-        <v>7623</v>
+        <v>7626</v>
       </c>
       <c r="R73" t="n">
-        <v>27.99784450019936</v>
+        <v>28.00886293565792</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -14553,13 +14553,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="O80" t="n">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="R80" t="n">
-        <v>19.51211033425562</v>
+        <v>19.49342057339906</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14712,10 +14712,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="O81" t="n">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>8083</v>
+        <v>8084</v>
       </c>
       <c r="O86" t="n">
-        <v>8083</v>
+        <v>8084</v>
       </c>
       <c r="R86" t="n">
-        <v>29.68733793717847</v>
+        <v>29.69101074899798</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -15671,13 +15671,13 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="O87" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="R87" t="n">
-        <v>18.3573106433179</v>
+        <v>18.37509873502654</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15830,10 +15830,10 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="O88" t="n">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
@@ -16064,13 +16064,13 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="O89" t="n">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="R89" t="n">
-        <v>21.42781082205371</v>
+        <v>21.40912106119715</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16223,10 +16223,10 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="O90" t="n">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>4981</v>
+        <v>5625</v>
       </c>
       <c r="O95" t="n">
-        <v>4981</v>
+        <v>5625</v>
       </c>
       <c r="R95" t="n">
-        <v>18.29427567302807</v>
+        <v>20.65956648479882</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>594</v>
+        <v>810</v>
       </c>
       <c r="O96" t="n">
-        <v>594</v>
+        <v>810</v>
       </c>
       <c r="R96" t="n">
-        <v>10.56612647493298</v>
+        <v>14.40835428399951</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>594</v>
+        <v>810</v>
       </c>
       <c r="O97" t="n">
-        <v>594</v>
+        <v>810</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>494833</v>
+        <v>495694</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>5625</v>
+        <v>5955</v>
       </c>
       <c r="O95" t="n">
-        <v>5625</v>
+        <v>5955</v>
       </c>
       <c r="R95" t="n">
-        <v>20.65956648479882</v>
+        <v>21.87159438524035</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>495694</v>
+        <v>496024</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -17182,13 +17182,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="O96" t="n">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="R96" t="n">
-        <v>14.40835428399951</v>
+        <v>15.24439459430566</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -17341,10 +17341,10 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="O97" t="n">
-        <v>810</v>
+        <v>857</v>
       </c>
       <c r="U97" t="inlineStr">
         <is>
@@ -17938,6 +17938,151 @@
         </is>
       </c>
       <c r="BC100" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>13669</v>
+      </c>
+      <c r="O101" t="n">
+        <v>13669</v>
+      </c>
+      <c r="R101" t="n">
+        <v>3.916220623682472</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -17976,7 +18121,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18204,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -18069,7 +18214,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -18121,7 +18266,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>496024</v>
+        <v>509740</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -13222,13 +13222,13 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="O73" t="n">
-        <v>7626</v>
+        <v>7627</v>
       </c>
       <c r="R73" t="n">
-        <v>28.00886293565792</v>
+        <v>28.01253574747744</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -15526,13 +15526,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>8084</v>
+        <v>8086</v>
       </c>
       <c r="O86" t="n">
-        <v>8084</v>
+        <v>8086</v>
       </c>
       <c r="R86" t="n">
-        <v>29.69101074899798</v>
+        <v>29.69835637263702</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -17037,13 +17037,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>5955</v>
+        <v>6255</v>
       </c>
       <c r="O95" t="n">
-        <v>5955</v>
+        <v>6255</v>
       </c>
       <c r="R95" t="n">
-        <v>21.87159438524035</v>
+        <v>22.97343793109629</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>509740</v>
+        <v>510043</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -1473,7 +1473,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1481,17 +1481,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1707,7 +1712,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1715,17 +1720,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1885,7 +1895,7 @@
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -2124,7 +2134,7 @@
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -2269,7 +2279,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -2277,17 +2287,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
@@ -2503,7 +2518,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2511,17 +2526,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -4085,7 +4105,7 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
@@ -4093,17 +4113,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS21" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
@@ -4319,7 +4344,7 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
@@ -4327,17 +4352,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS22" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
@@ -4497,7 +4527,7 @@
         </is>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
@@ -4736,7 +4766,7 @@
         </is>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
@@ -4881,7 +4911,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -4889,17 +4919,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5115,7 +5150,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5123,17 +5158,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -6549,7 +6589,7 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
@@ -6557,17 +6597,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS35" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
@@ -6783,7 +6828,7 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
@@ -6791,17 +6836,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS36" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
@@ -6961,7 +7011,7 @@
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
@@ -7200,7 +7250,7 @@
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
@@ -7345,7 +7395,7 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
@@ -7353,17 +7403,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS39" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -7579,7 +7634,7 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ40" t="inlineStr">
@@ -7587,17 +7642,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS40" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -9010,7 +9070,7 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
@@ -9018,17 +9078,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS49" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
@@ -9244,7 +9309,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -9252,17 +9317,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9422,7 +9492,7 @@
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
@@ -9661,7 +9731,7 @@
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
@@ -9806,7 +9876,7 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
@@ -9814,17 +9884,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS53" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -10040,7 +10115,7 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
@@ -10048,17 +10123,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS54" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -11326,7 +11406,7 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ62" t="inlineStr">
@@ -11334,17 +11414,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS62" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
@@ -11560,7 +11645,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -11568,17 +11653,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -11738,7 +11828,7 @@
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -11977,7 +12067,7 @@
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
@@ -12122,7 +12212,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -12130,17 +12220,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -12356,7 +12451,7 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ67" t="inlineStr">
@@ -12364,17 +12459,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS67" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV67" t="inlineStr">
@@ -13787,7 +13887,7 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ76" t="inlineStr">
@@ -13795,17 +13895,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR76" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS76" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
@@ -14021,7 +14126,7 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ77" t="inlineStr">
@@ -14029,17 +14134,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS77" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV77" t="inlineStr">
@@ -14199,7 +14309,7 @@
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
@@ -14438,7 +14548,7 @@
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU79" t="inlineStr">
         <is>
@@ -14583,7 +14693,7 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
@@ -14591,17 +14701,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR80" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS80" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
@@ -14817,7 +14932,7 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
@@ -14825,17 +14940,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS81" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
@@ -15701,7 +15821,7 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
@@ -15709,17 +15829,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR87" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS87" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
@@ -15935,7 +16060,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -15943,17 +16068,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -16094,7 +16224,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -16102,17 +16232,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -16328,7 +16463,7 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
@@ -16336,17 +16471,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS90" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
@@ -17037,13 +17177,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>6255</v>
+        <v>6383</v>
       </c>
       <c r="O95" t="n">
-        <v>6255</v>
+        <v>6383</v>
       </c>
       <c r="R95" t="n">
-        <v>22.97343793109629</v>
+        <v>23.44355784399482</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17212,7 +17352,7 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
@@ -17220,17 +17360,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR96" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS96" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
@@ -17446,7 +17591,7 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
@@ -17454,17 +17599,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS97" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
@@ -18266,7 +18416,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>510043</v>
+        <v>510171</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -11337,12 +11337,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -11376,100 +11376,81 @@
         </is>
       </c>
       <c r="N62" t="n">
-        <v>834</v>
+        <v>1007</v>
       </c>
       <c r="O62" t="n">
-        <v>834</v>
+        <v>1007</v>
       </c>
       <c r="R62" t="n">
-        <v>14.83526848500691</v>
+        <v>11.17920273078948</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA62" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ62" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR62" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS62" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -11496,7 +11477,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11545,98 +11526,23 @@
       <c r="O63" t="n">
         <v>834</v>
       </c>
+      <c r="R63" t="n">
+        <v>14.83526848500691</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y63" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG63" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN63" t="b">
-        <v>1</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -11735,17 +11641,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -11779,22 +11685,39 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>125</v>
+        <v>834</v>
       </c>
       <c r="O64" t="n">
-        <v>125</v>
-      </c>
-      <c r="R64" t="n">
-        <v>31.0691001642934</v>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>834</v>
       </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -11802,6 +11725,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN64" t="b">
+        <v>1</v>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -11824,11 +11805,11 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1350</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
@@ -11837,42 +11818,42 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -11899,7 +11880,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -11948,98 +11929,23 @@
       <c r="O65" t="n">
         <v>125</v>
       </c>
+      <c r="R65" t="n">
+        <v>31.0691001642934</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
           <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_STI</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>Klamydía</t>
-        </is>
-      </c>
-      <c r="Y65" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>laboratory_and_registry_diagnoses</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG65" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>IS_DOH_sti_current</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN65" t="b">
-        <v>1</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -12138,17 +12044,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -12182,22 +12088,39 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>2043</v>
+        <v>125</v>
       </c>
       <c r="O66" t="n">
-        <v>2043</v>
-      </c>
-      <c r="R66" t="n">
-        <v>19.09159071498287</v>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
       </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC_IS_DOH_STI</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Klamydía</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -12205,6 +12128,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>country:IS:national</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>IS_DOH_sti_current</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN66" t="b">
+        <v>1</v>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -12217,7 +12198,7 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR66" t="inlineStr">
@@ -12227,55 +12208,55 @@
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12283,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12351,98 +12332,23 @@
       <c r="O67" t="n">
         <v>2043</v>
       </c>
+      <c r="R67" t="n">
+        <v>19.09159071498287</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X67" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y67" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG67" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN67" t="b">
-        <v>1</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -12541,17 +12447,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -12576,7 +12482,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -12585,84 +12491,175 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>13174</v>
+        <v>2043</v>
       </c>
       <c r="O68" t="n">
-        <v>13174</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="n">
-        <v>3.774401236110388</v>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2043</v>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN68" t="b">
+        <v>1</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR68" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS68" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV68" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -12724,7 +12721,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -12733,16 +12730,16 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>9872</v>
+        <v>13174</v>
       </c>
       <c r="O69" t="n">
-        <v>9872</v>
+        <v>13174</v>
       </c>
       <c r="Q69" t="n">
         <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.828365644669937</v>
+        <v>3.774401236110388</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -12872,7 +12869,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -12881,16 +12878,16 @@
         </is>
       </c>
       <c r="N70" t="n">
-        <v>13193</v>
+        <v>9872</v>
       </c>
       <c r="O70" t="n">
-        <v>13193</v>
+        <v>9872</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.77984480856265</v>
+        <v>2.828365644669937</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
@@ -13020,7 +13017,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -13029,16 +13026,16 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>3506</v>
+        <v>13193</v>
       </c>
       <c r="O71" t="n">
-        <v>3506</v>
+        <v>13193</v>
       </c>
       <c r="Q71" t="n">
         <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>1.004482369348946</v>
+        <v>3.77984480856265</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -13168,7 +13165,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -13177,13 +13174,16 @@
         </is>
       </c>
       <c r="N72" t="n">
-        <v>6938</v>
+        <v>3506</v>
       </c>
       <c r="O72" t="n">
-        <v>6938</v>
+        <v>3506</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>1.9877634565154</v>
+        <v>1.004482369348946</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
@@ -13283,12 +13283,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -13313,22 +13313,22 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>7627</v>
+        <v>6938</v>
       </c>
       <c r="O73" t="n">
-        <v>7627</v>
+        <v>6938</v>
       </c>
       <c r="R73" t="n">
-        <v>28.01253574747744</v>
+        <v>1.9877634565154</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
@@ -13361,42 +13361,42 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -13428,12 +13428,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -13467,67 +13467,56 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>3092</v>
+        <v>7627</v>
       </c>
       <c r="O74" t="n">
-        <v>3092</v>
+        <v>7627</v>
+      </c>
+      <c r="R74" t="n">
+        <v>28.01253574747744</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>missing_population</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ74" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR74" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
@@ -13537,17 +13526,17 @@
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -13579,17 +13568,17 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>CA-ON</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ontario, Canada</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -13623,145 +13612,53 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>3092</v>
+        <v>88</v>
       </c>
       <c r="O75" t="n">
-        <v>3092</v>
-      </c>
-      <c r="U75" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V75" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC_CA_ON_PHO_IDTO</t>
-        </is>
-      </c>
-      <c r="X75" t="inlineStr">
-        <is>
-          <t>Chlamydial Infections</t>
-        </is>
-      </c>
-      <c r="Y75" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>country:CA-ON:national</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
+        <v>88</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP75" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR75" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE75" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF75" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG75" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>PHO_IDTO_2026_07</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN75" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP75" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ75" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS75" t="inlineStr">
-        <is>
-          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series.</t>
-        </is>
-      </c>
-      <c r="AV75" t="inlineStr">
-        <is>
-          <t>pho_idto_monthly</t>
-        </is>
-      </c>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr">
@@ -13771,17 +13668,17 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>pho_idto_monthly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>Public Health Ontario IDTO Monthly</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -13818,12 +13715,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -13857,100 +13754,78 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>910</v>
+        <v>2164</v>
       </c>
       <c r="O76" t="n">
-        <v>910</v>
-      </c>
-      <c r="R76" t="n">
-        <v>16.18716345486365</v>
+        <v>2164</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ76" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR76" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS76" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -13977,17 +13852,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -14021,175 +13896,78 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>910</v>
+        <v>234</v>
       </c>
       <c r="O77" t="n">
-        <v>910</v>
-      </c>
-      <c r="U77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W77" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
+        <v>234</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR77" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN77" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS77" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT77" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV77" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14221,12 +13999,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -14260,75 +14038,53 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>153</v>
+        <v>2017</v>
       </c>
       <c r="O78" t="n">
-        <v>153</v>
-      </c>
-      <c r="R78" t="n">
-        <v>38.02857860109512</v>
+        <v>2017</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ78" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR78" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS78" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>is_doh_annual</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr">
@@ -14338,22 +14094,22 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14380,17 +14136,17 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>IS</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -14424,150 +14180,53 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>153</v>
+        <v>397</v>
       </c>
       <c r="O79" t="n">
-        <v>153</v>
-      </c>
-      <c r="U79" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>SRC_IS_DOH_STI</t>
-        </is>
-      </c>
-      <c r="X79" t="inlineStr">
-        <is>
-          <t>Klamydía</t>
-        </is>
-      </c>
-      <c r="Y79" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>laboratory_and_registry_diagnoses</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>country:IS:national</t>
-        </is>
-      </c>
-      <c r="AD79" t="inlineStr">
+        <v>397</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP79" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR79" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE79" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF79" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG79" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>IS_DOH_sti_current</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN79" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP79" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ79" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AT79" t="n">
-        <v>5</v>
-      </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV79" t="inlineStr">
-        <is>
-          <t>is_doh_annual</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr">
@@ -14577,22 +14236,22 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
         <is>
-          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14624,12 +14283,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -14663,100 +14322,78 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>2086</v>
+        <v>114</v>
       </c>
       <c r="O80" t="n">
-        <v>2086</v>
-      </c>
-      <c r="R80" t="n">
-        <v>19.49342057339906</v>
+        <v>114</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="AA80" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ80" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS80" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -14783,17 +14420,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -14827,175 +14464,78 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>2086</v>
+        <v>1662</v>
       </c>
       <c r="O81" t="n">
-        <v>2086</v>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X81" t="inlineStr">
-        <is>
-          <t>Klamydiainfektion</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD81" t="inlineStr">
+        <v>1662</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP81" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR81" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE81" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF81" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG81" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN81" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP81" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ81" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS81" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
-        </is>
-      </c>
-      <c r="AT81" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
-        </is>
-      </c>
-      <c r="AV81" t="inlineStr">
-        <is>
-          <t>fohm_sminet</t>
-        </is>
-      </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15027,12 +14567,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15057,7 +14597,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -15066,17 +14606,14 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>12263</v>
+        <v>951</v>
       </c>
       <c r="O82" t="n">
-        <v>12263</v>
-      </c>
-      <c r="R82" t="n">
-        <v>3.513396262215097</v>
+        <v>951</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -15105,42 +14642,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15172,12 +14709,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -15202,7 +14739,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -15211,81 +14748,92 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>13313</v>
+        <v>3092</v>
       </c>
       <c r="O83" t="n">
-        <v>13313</v>
-      </c>
-      <c r="R83" t="n">
-        <v>3.814225266155883</v>
+        <v>3092</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ83" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15312,17 +14860,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -15347,7 +14895,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -15356,81 +14904,170 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>12631</v>
+        <v>3092</v>
       </c>
       <c r="O84" t="n">
-        <v>12631</v>
-      </c>
-      <c r="R84" t="n">
-        <v>3.618829665501011</v>
-      </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3092</v>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Chlamydial Infections</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD84" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE84" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG84" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary Chlamydia trachomatis infection notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN84" t="b">
+        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS84" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ84" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_CHLAMYDIA_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB84" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC84" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -15462,12 +15099,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -15492,7 +15129,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -15501,81 +15138,100 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>10277</v>
+        <v>910</v>
       </c>
       <c r="O85" t="n">
-        <v>10277</v>
+        <v>910</v>
       </c>
       <c r="R85" t="n">
-        <v>2.944399689047097</v>
+        <v>16.18716345486365</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ85" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR85" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15602,17 +15258,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -15637,90 +15293,184 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>8086</v>
+        <v>910</v>
       </c>
       <c r="O86" t="n">
-        <v>8086</v>
-      </c>
-      <c r="R86" t="n">
-        <v>29.69835637263702</v>
-      </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>910</v>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD86" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE86" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG86" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN86" t="b">
+        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ86" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS86" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS86" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15502,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -15782,22 +15532,22 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N87" t="n">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="O87" t="n">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="R87" t="n">
-        <v>18.37509873502654</v>
+        <v>38.02857860109512</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15806,7 +15556,7 @@
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -15836,11 +15586,11 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
@@ -15849,42 +15599,42 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -15916,12 +15666,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>IS</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -15946,38 +15696,38 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="O88" t="n">
-        <v>1033</v>
+        <v>153</v>
       </c>
       <c r="U88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_IS_DOH_STI</t>
         </is>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Chlamydia</t>
+          <t>Klamydía</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
@@ -15987,7 +15737,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>laboratory_and_registry_diagnoses</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -16002,7 +15752,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:IS:national</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr">
@@ -16037,17 +15787,17 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>IS_DOH_sti_current</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+          <t>Monthly diagnoses published in the national Iceland STI dashboard.</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN88" t="b">
@@ -16075,11 +15825,11 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1350</t>
+          <t>SER_IS_DOH_STI_CHLAMYDIA_MONTHLY</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
@@ -16088,42 +15838,42 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>is_doh_annual</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Iceland Directorate of Health Annual Dashboard</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>is_doh_annual; is_doh_sti; is_doh_respiratory; is_doh_history; is_doh_legacy_icd</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Iceland Directorate of Health Annual Dashboard; Iceland Directorate of Health STI Dashboard; Iceland Directorate of Health Respiratory Dashboard; Iceland Directorate of Health Historical Registry; Iceland Directorate of Health Legacy ICD Monthly</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/respiratory-tract-infections; https://island.is/en/smitsjukdomar-tolur; https://island.is/en/smitsjukdomar-tolur</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi; microsoft_bi; microsoft_bi; official_excel; official_excel</t>
         </is>
       </c>
     </row>
@@ -16185,22 +15935,22 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2291</v>
+        <v>2086</v>
       </c>
       <c r="O89" t="n">
-        <v>2291</v>
+        <v>2086</v>
       </c>
       <c r="R89" t="n">
-        <v>21.40912106119715</v>
+        <v>19.49342057339906</v>
       </c>
       <c r="S89" t="inlineStr">
         <is>
@@ -16349,19 +16099,19 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N90" t="n">
-        <v>2291</v>
+        <v>2086</v>
       </c>
       <c r="O90" t="n">
-        <v>2291</v>
+        <v>2086</v>
       </c>
       <c r="U90" t="inlineStr">
         <is>
@@ -16588,22 +16338,22 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N91" t="n">
-        <v>10203</v>
+        <v>12263</v>
       </c>
       <c r="O91" t="n">
-        <v>10203</v>
+        <v>12263</v>
       </c>
       <c r="R91" t="n">
-        <v>2.923198406864604</v>
+        <v>3.513396262215097</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -16733,22 +16483,22 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N92" t="n">
-        <v>13432</v>
+        <v>13313</v>
       </c>
       <c r="O92" t="n">
-        <v>13432</v>
+        <v>13313</v>
       </c>
       <c r="R92" t="n">
-        <v>3.848319219935838</v>
+        <v>3.814225266155883</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -16878,22 +16628,22 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N93" t="n">
-        <v>13446</v>
+        <v>12631</v>
       </c>
       <c r="O93" t="n">
-        <v>13446</v>
+        <v>12631</v>
       </c>
       <c r="R93" t="n">
-        <v>3.852330273321715</v>
+        <v>3.618829665501011</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -17023,22 +16773,22 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N94" t="n">
-        <v>14046</v>
+        <v>10277</v>
       </c>
       <c r="O94" t="n">
-        <v>14046</v>
+        <v>10277</v>
       </c>
       <c r="R94" t="n">
-        <v>4.024232561287879</v>
+        <v>2.944399689047097</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -17168,22 +16918,22 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>6383</v>
+        <v>8108</v>
       </c>
       <c r="O95" t="n">
-        <v>6383</v>
+        <v>8108</v>
       </c>
       <c r="R95" t="n">
-        <v>23.44355784399482</v>
+        <v>29.77915823266646</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -17283,12 +17033,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -17313,109 +17063,87 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>857</v>
+        <v>75</v>
       </c>
       <c r="O96" t="n">
-        <v>857</v>
-      </c>
-      <c r="R96" t="n">
-        <v>15.24439459430566</v>
+        <v>75</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U96" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AA96" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ96" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17442,17 +17170,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -17477,184 +17205,87 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>857</v>
+        <v>2227</v>
       </c>
       <c r="O97" t="n">
-        <v>857</v>
-      </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="V97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X97" t="inlineStr">
-        <is>
-          <t>Chlamydia</t>
-        </is>
-      </c>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD97" t="inlineStr">
+        <v>2227</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
+      <c r="AT97" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE97" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF97" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG97" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH97" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
-        </is>
-      </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN97" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP97" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1350</t>
-        </is>
-      </c>
-      <c r="AT97" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV97" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17686,12 +17317,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -17716,26 +17347,23 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>15153</v>
+        <v>184</v>
       </c>
       <c r="O98" t="n">
-        <v>15153</v>
-      </c>
-      <c r="R98" t="n">
-        <v>4.341392282585449</v>
+        <v>184</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -17764,42 +17392,42 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17831,12 +17459,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -17861,26 +17489,23 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N99" t="n">
-        <v>14684</v>
+        <v>2132</v>
       </c>
       <c r="O99" t="n">
-        <v>14684</v>
-      </c>
-      <c r="R99" t="n">
-        <v>4.207021994158565</v>
+        <v>2132</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -17909,42 +17534,42 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17976,12 +17601,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -18006,26 +17631,23 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>14554</v>
+        <v>466</v>
       </c>
       <c r="O100" t="n">
-        <v>14554</v>
-      </c>
-      <c r="R100" t="n">
-        <v>4.169776498432563</v>
+        <v>466</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -18054,42 +17676,42 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18121,12 +17743,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -18151,26 +17773,23 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>13669</v>
+        <v>113</v>
       </c>
       <c r="O101" t="n">
-        <v>13669</v>
-      </c>
-      <c r="R101" t="n">
-        <v>3.916220623682472</v>
+        <v>113</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -18199,42 +17818,4669 @@
       </c>
       <c r="AV101" t="inlineStr">
         <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>1873</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1873</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>1019</v>
+      </c>
+      <c r="O103" t="n">
+        <v>1019</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA103" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB103" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>1033</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1033</v>
+      </c>
+      <c r="R104" t="n">
+        <v>18.37509873502654</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1033</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1033</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>2289</v>
+      </c>
+      <c r="O106" t="n">
+        <v>2289</v>
+      </c>
+      <c r="R106" t="n">
+        <v>21.39043130034058</v>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP106" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ106" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS106" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AT106" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU106" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV106" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA106" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB106" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC106" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>2289</v>
+      </c>
+      <c r="O107" t="n">
+        <v>2289</v>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X107" t="inlineStr">
+        <is>
+          <t>Klamydiainfektion</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD107" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE107" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG107" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM source-defined chlamydia category.</t>
+        </is>
+      </c>
+      <c r="AM107" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN107" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP107" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ107" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR107" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS107" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CHLAMYDIA</t>
+        </is>
+      </c>
+      <c r="AT107" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU107" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV107" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA107" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB107" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC107" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>2026-07-04</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>10203</v>
+      </c>
+      <c r="O108" t="n">
+        <v>10203</v>
+      </c>
+      <c r="R108" t="n">
+        <v>2.923198406864604</v>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP108" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR108" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS108" t="inlineStr"/>
+      <c r="AT108" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU108" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV108" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW101" t="inlineStr">
+      <c r="AW108" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
+      <c r="AX108" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr">
+      <c r="AY108" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
+      <c r="AZ108" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA101" t="inlineStr">
+      <c r="BA108" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB101" t="inlineStr">
+      <c r="BB108" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC101" t="inlineStr">
+      <c r="BC108" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>13432</v>
+      </c>
+      <c r="O109" t="n">
+        <v>13432</v>
+      </c>
+      <c r="R109" t="n">
+        <v>3.848319219935838</v>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP109" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr"/>
+      <c r="AT109" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU109" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV109" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA109" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB109" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC109" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>13446</v>
+      </c>
+      <c r="O110" t="n">
+        <v>13446</v>
+      </c>
+      <c r="R110" t="n">
+        <v>3.852330273321715</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP110" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr"/>
+      <c r="AT110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU110" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV110" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA110" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB110" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC110" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>14046</v>
+      </c>
+      <c r="O111" t="n">
+        <v>14046</v>
+      </c>
+      <c r="R111" t="n">
+        <v>4.024232561287879</v>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP111" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR111" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS111" t="inlineStr"/>
+      <c r="AT111" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU111" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV111" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA111" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB111" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC111" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>7203</v>
+      </c>
+      <c r="O112" t="n">
+        <v>7203</v>
+      </c>
+      <c r="R112" t="n">
+        <v>26.45526353600104</v>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS112" t="inlineStr"/>
+      <c r="AT112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU112" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA112" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB112" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC112" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>AU-ACT</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Australian Capital Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N113" t="n">
+        <v>73</v>
+      </c>
+      <c r="O113" t="n">
+        <v>73</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP113" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR113" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS113" t="inlineStr"/>
+      <c r="AT113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU113" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA113" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Australian Capital Territory</t>
+        </is>
+      </c>
+      <c r="BB113" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC113" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>AU-NSW</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>New South Wales, Australia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1939</v>
+      </c>
+      <c r="O114" t="n">
+        <v>1939</v>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP114" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS114" t="inlineStr"/>
+      <c r="AT114" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU114" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA114" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — New South Wales</t>
+        </is>
+      </c>
+      <c r="BB114" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC114" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>AU-NT</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Northern Territory, Australia</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N115" t="n">
+        <v>51</v>
+      </c>
+      <c r="O115" t="n">
+        <v>51</v>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP115" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS115" t="inlineStr"/>
+      <c r="AT115" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU115" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA115" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Northern Territory</t>
+        </is>
+      </c>
+      <c r="BB115" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC115" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>AU-QLD</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Queensland, Australia</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1738</v>
+      </c>
+      <c r="O116" t="n">
+        <v>1738</v>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP116" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR116" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS116" t="inlineStr"/>
+      <c r="AT116" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU116" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA116" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Queensland</t>
+        </is>
+      </c>
+      <c r="BB116" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC116" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>AU-SA</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>South Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>345</v>
+      </c>
+      <c r="O117" t="n">
+        <v>345</v>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP117" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR117" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS117" t="inlineStr"/>
+      <c r="AT117" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU117" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — South Australia</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>AU-TAS</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Tasmania, Australia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>93</v>
+      </c>
+      <c r="O118" t="n">
+        <v>93</v>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP118" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
+      <c r="AT118" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU118" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Tasmania</t>
+        </is>
+      </c>
+      <c r="BB118" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC118" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>AU-VIC</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Victoria, Australia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N119" t="n">
+        <v>1335</v>
+      </c>
+      <c r="O119" t="n">
+        <v>1335</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Victoria</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>AU-WA</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Western Australia, Australia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N120" t="n">
+        <v>851</v>
+      </c>
+      <c r="O120" t="n">
+        <v>851</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP120" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS120" t="inlineStr"/>
+      <c r="AT120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU120" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA120" t="inlineStr">
+        <is>
+          <t>Australia NINDSS — Western Australia</t>
+        </is>
+      </c>
+      <c r="BB120" t="inlineStr">
+        <is>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+        </is>
+      </c>
+      <c r="BC120" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N121" t="n">
+        <v>1066</v>
+      </c>
+      <c r="O121" t="n">
+        <v>1066</v>
+      </c>
+      <c r="R121" t="n">
+        <v>18.96210576141171</v>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP121" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ121" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS121" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU121" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV121" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA121" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB121" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC121" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N122" t="n">
+        <v>1066</v>
+      </c>
+      <c r="O122" t="n">
+        <v>1066</v>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD122" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE122" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG122" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH122" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM122" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN122" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP122" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ122" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS122" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT122" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU122" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA122" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB122" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC122" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>15153</v>
+      </c>
+      <c r="O123" t="n">
+        <v>15153</v>
+      </c>
+      <c r="R123" t="n">
+        <v>4.341392282585449</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP123" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS123" t="inlineStr"/>
+      <c r="AT123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU123" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV123" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA123" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB123" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC123" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>14684</v>
+      </c>
+      <c r="O124" t="n">
+        <v>14684</v>
+      </c>
+      <c r="R124" t="n">
+        <v>4.207021994158565</v>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP124" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR124" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr"/>
+      <c r="AT124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU124" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV124" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA124" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB124" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC124" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>14554</v>
+      </c>
+      <c r="O125" t="n">
+        <v>14554</v>
+      </c>
+      <c r="R125" t="n">
+        <v>4.169776498432563</v>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP125" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR125" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr"/>
+      <c r="AT125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU125" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV125" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA125" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB125" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC125" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>13669</v>
+      </c>
+      <c r="O126" t="n">
+        <v>13669</v>
+      </c>
+      <c r="R126" t="n">
+        <v>3.916220623682472</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP126" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr"/>
+      <c r="AT126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV126" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA126" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB126" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC126" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>16595</v>
+      </c>
+      <c r="O127" t="n">
+        <v>16595</v>
+      </c>
+      <c r="R127" t="n">
+        <v>4.754530781330795</v>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP127" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr"/>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV127" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA127" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB127" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC127" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N128" t="n">
+        <v>112</v>
+      </c>
+      <c r="O128" t="n">
+        <v>112</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.4113549237862165</v>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP128" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR128" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS128" t="inlineStr"/>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA128" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB128" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC128" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N129" t="n">
+        <v>18</v>
+      </c>
+      <c r="O129" t="n">
+        <v>18</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.3201856507555447</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP129" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ129" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR129" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS129" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT129" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU129" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV129" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA129" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB129" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC129" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>chlamydia-trachomatis-infection</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>D094</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Chlamydia trachomatis infection</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>沙眼衣原体感染</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>18</v>
+      </c>
+      <c r="O130" t="n">
+        <v>18</v>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Chlamydia</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1350.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP130" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ130" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS130" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1350</t>
+        </is>
+      </c>
+      <c r="AT130" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU130" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA130" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB130" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC130" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18271,7 +22517,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -18354,7 +22600,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -18364,7 +22610,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11">
@@ -18384,7 +22630,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -18416,7 +22662,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>510171</v>
+        <v>551093</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d094/2026-2029.xlsx
+++ b/diseases/d094/2026-2029.xlsx
@@ -16927,13 +16927,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8108</v>
+        <v>8110</v>
       </c>
       <c r="O95" t="n">
-        <v>8108</v>
+        <v>8110</v>
       </c>
       <c r="R95" t="n">
-        <v>29.77915823266646</v>
+        <v>29.7865038563055</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19594,13 +19594,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>7203</v>
+        <v>7290</v>
       </c>
       <c r="O112" t="n">
-        <v>7203</v>
+        <v>7290</v>
       </c>
       <c r="R112" t="n">
-        <v>26.45526353600104</v>
+        <v>26.77479816429927</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -20875,13 +20875,13 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="O121" t="n">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="R121" t="n">
-        <v>18.96210576141171</v>
+        <v>19.42459614583638</v>
       </c>
       <c r="S121" t="inlineStr">
         <is>
@@ -21039,10 +21039,10 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="O122" t="n">
-        <v>1066</v>
+        <v>1092</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
@@ -22003,13 +22003,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>112</v>
+        <v>376</v>
       </c>
       <c r="O128" t="n">
-        <v>112</v>
+        <v>376</v>
       </c>
       <c r="R128" t="n">
-        <v>0.4113549237862165</v>
+        <v>1.380977244139441</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -22148,13 +22148,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O129" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="R129" t="n">
-        <v>0.3201856507555447</v>
+        <v>0.7293117600542963</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22312,10 +22312,10 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="O130" t="n">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>551093</v>
+        <v>551495</v>
       </c>
     </row>
     <row r="16">
